--- a/Book2.xlsx
+++ b/Book2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\umezu\開発\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6599E3D9-4EC8-47E8-BD0B-FA409B1B48A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC8B4D2-57DB-468D-AC53-5EC1D6B49E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{309D370C-6998-433A-93E9-5EAD6DB5690C}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>終了</t>
     <rPh sb="0" eb="2">
@@ -101,6 +101,16 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>注文登録画面</t>
+    <rPh sb="0" eb="4">
+      <t>チュウモントウロク</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -304,11 +314,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -667,11 +677,11 @@
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="7"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="8"/>
@@ -689,9 +699,11 @@
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="7"/>
       <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
+      <c r="C6" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
       <c r="H6" s="8"/>
@@ -778,7 +790,7 @@
       <c r="H14" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="13" t="s">
         <v>3</v>
       </c>
       <c r="B16" t="s">
@@ -786,7 +798,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="13" t="s">
         <v>5</v>
       </c>
       <c r="B17" t="s">
@@ -794,7 +806,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="13" t="s">
         <v>7</v>
       </c>
       <c r="B18" t="s">
@@ -802,8 +814,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C6:E6"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
